--- a/output/top100_by_position.xlsx
+++ b/output/top100_by_position.xlsx
@@ -18772,12 +18772,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Deuce Vaughn</t>
+          <t>Jeff Wilson</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -18786,7 +18786,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>21.853</v>
+        <v>23.049</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -18798,19 +18798,19 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>44.23</v>
+        <v>57.09</v>
       </c>
       <c r="I100" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="J100" t="n">
-        <v>2.93</v>
+        <v>2.36</v>
       </c>
       <c r="K100" t="n">
-        <v>22.6</v>
+        <v>17.1</v>
       </c>
       <c r="L100" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -18879,18 +18879,18 @@
         <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Deuce Vaughn</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>20.582</v>
+        <v>21.853</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -18911,32 +18911,32 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>47.86</v>
+        <v>44.23</v>
       </c>
       <c r="I101" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="K101" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
         <v>0.02</v>
       </c>
-      <c r="J101" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K101" t="n">
-        <v>24.46</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
@@ -18992,7 +18992,7 @@
         <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>129</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -38482,7 +38482,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -49317,7 +49317,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -49329,19 +49329,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="n">
         <v>116</v>
       </c>
-      <c r="G3" t="n">
-        <v>112</v>
-      </c>
       <c r="H3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I3" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -49353,7 +49353,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -49410,7 +49410,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -49420,7 +49420,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -49438,13 +49438,13 @@
         <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I4" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J4" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K4" t="n">
         <v>44</v>
@@ -49513,7 +49513,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">

--- a/output/top100_by_position.xlsx
+++ b/output/top100_by_position.xlsx
@@ -10528,7 +10528,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -14478,12 +14478,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ameer Abdullah</t>
+          <t>Trey Sermon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -14492,7 +14492,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>68.54220000000001</v>
+        <v>64.52</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -14504,22 +14504,22 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>171.05</v>
+        <v>282.5999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>0.74</v>
+        <v>1.860000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>19.03</v>
+        <v>8.359999999999998</v>
       </c>
       <c r="K62" t="n">
-        <v>144.04</v>
+        <v>62.50000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
       <c r="M62" t="n">
-        <v>24.57999999999999</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -14528,7 +14528,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -14585,18 +14585,18 @@
         <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Trey Sermon</t>
+          <t>Zamir White</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>64.52</v>
+        <v>61.48100000000001</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -14617,19 +14617,19 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>282.5999999999999</v>
+        <v>258.77</v>
       </c>
       <c r="I63" t="n">
-        <v>1.860000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="J63" t="n">
-        <v>8.359999999999998</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>62.50000000000001</v>
+        <v>57.63999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -14641,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -14698,18 +14698,18 @@
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zamir White</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -14718,7 +14718,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>61.48100000000001</v>
+        <v>61.004</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -14730,19 +14730,19 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>258.77</v>
+        <v>225.51</v>
       </c>
       <c r="I64" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>9.999999999999998</v>
       </c>
       <c r="K64" t="n">
-        <v>57.63999999999999</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>0.34</v>
+        <v>0.4500000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -14754,7 +14754,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.36</v>
+        <v>0.3799999999999999</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -14811,18 +14811,18 @@
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Carson Steele</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>61.004</v>
+        <v>60.456</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -14843,19 +14843,19 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>225.51</v>
+        <v>243.48</v>
       </c>
       <c r="I65" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="J65" t="n">
-        <v>9.999999999999998</v>
+        <v>7.879999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>72.43000000000001</v>
+        <v>59.47999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>0.4500000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -14867,7 +14867,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.3799999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -14924,18 +14924,18 @@
         <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Carson Steele</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>60.456</v>
+        <v>58.75000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -14956,19 +14956,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>243.48</v>
+        <v>202.3</v>
       </c>
       <c r="I66" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="J66" t="n">
-        <v>7.879999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="K66" t="n">
-        <v>59.47999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="L66" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -14980,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -15037,18 +15037,18 @@
         <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Miles Sanders</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>58.75000000000001</v>
+        <v>58.72</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -15069,19 +15069,19 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>202.3</v>
+        <v>207.23</v>
       </c>
       <c r="I67" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="J67" t="n">
-        <v>10.88</v>
+        <v>12.43</v>
       </c>
       <c r="K67" t="n">
-        <v>81.7</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -15093,7 +15093,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -15150,18 +15150,18 @@
         <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Miles Sanders</t>
+          <t>Audric Estime</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15170,7 +15170,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>58.72</v>
+        <v>58.621</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -15182,19 +15182,19 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>207.23</v>
+        <v>254.06</v>
       </c>
       <c r="I68" t="n">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
-        <v>12.43</v>
+        <v>6.06</v>
       </c>
       <c r="K68" t="n">
-        <v>91.56999999999999</v>
+        <v>44.45</v>
       </c>
       <c r="L68" t="n">
-        <v>0.31</v>
+        <v>0.09</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -15206,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.93</v>
+        <v>0.17</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -15263,18 +15263,18 @@
         <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>73</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Audric Estime</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15283,7 +15283,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>58.621</v>
+        <v>57.455</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -15295,19 +15295,19 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>254.06</v>
+        <v>232.1</v>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="J69" t="n">
-        <v>6.06</v>
+        <v>7.829999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>44.45</v>
+        <v>52.35</v>
       </c>
       <c r="L69" t="n">
-        <v>0.09</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -15319,7 +15319,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.17</v>
+        <v>0.6100000000000001</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -15376,18 +15376,18 @@
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Jeremy McNichols</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>57.455</v>
+        <v>55.76500000000001</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -15408,19 +15408,19 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>232.1</v>
+        <v>223.27</v>
       </c>
       <c r="I70" t="n">
-        <v>1.55</v>
+        <v>0.8099999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>7.829999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="K70" t="n">
-        <v>52.35</v>
+        <v>73.48000000000002</v>
       </c>
       <c r="L70" t="n">
-        <v>0.6200000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -15432,7 +15432,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.6100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -15489,18 +15489,18 @@
         <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jeremy McNichols</t>
+          <t>Khalil Herbert</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15509,7 +15509,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>55.76500000000001</v>
+        <v>54.40500000000001</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -15521,19 +15521,19 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>223.27</v>
+        <v>181.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8099999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="J71" t="n">
-        <v>10.04</v>
+        <v>7.489999999999999</v>
       </c>
       <c r="K71" t="n">
-        <v>73.48000000000002</v>
+        <v>53.88</v>
       </c>
       <c r="L71" t="n">
-        <v>0.27</v>
+        <v>0.7700000000000001</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -15545,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -15602,18 +15602,18 @@
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Khalil Herbert</t>
+          <t>Pierre Strong</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15622,7 +15622,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>54.40500000000001</v>
+        <v>50.786</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -15634,19 +15634,19 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>181.17</v>
+        <v>108.33</v>
       </c>
       <c r="I72" t="n">
-        <v>1.66</v>
+        <v>0.8100000000000002</v>
       </c>
       <c r="J72" t="n">
-        <v>7.489999999999999</v>
+        <v>13.96</v>
       </c>
       <c r="K72" t="n">
-        <v>53.88</v>
+        <v>102.83</v>
       </c>
       <c r="L72" t="n">
-        <v>0.7700000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -15658,7 +15658,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -15715,18 +15715,18 @@
         <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pierre Strong</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15735,7 +15735,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>50.786</v>
+        <v>48.151</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -15747,19 +15747,19 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>108.33</v>
+        <v>213.43</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8100000000000002</v>
+        <v>1.55</v>
       </c>
       <c r="J73" t="n">
-        <v>13.96</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>102.83</v>
+        <v>32.58</v>
       </c>
       <c r="L73" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -15771,7 +15771,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
@@ -15828,18 +15828,18 @@
         <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>D'Ernest Johnson</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>48.151</v>
+        <v>47.369</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -15860,19 +15860,19 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>213.43</v>
+        <v>153.49</v>
       </c>
       <c r="I74" t="n">
-        <v>1.55</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>10.39</v>
       </c>
       <c r="K74" t="n">
-        <v>32.58</v>
+        <v>79.69999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -15941,18 +15941,18 @@
         <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D'Ernest Johnson</t>
+          <t>Eric Gray</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>47.369</v>
+        <v>47.35800000000001</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -15973,19 +15973,19 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>153.49</v>
+        <v>116.46</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.8200000000000003</v>
       </c>
       <c r="J75" t="n">
-        <v>10.39</v>
+        <v>10.25</v>
       </c>
       <c r="K75" t="n">
-        <v>79.69999999999999</v>
+        <v>75.02000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>0.28</v>
+        <v>0.64</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -16054,18 +16054,18 @@
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Eric Gray</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -16074,7 +16074,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>47.35800000000001</v>
+        <v>47.032</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -16086,19 +16086,19 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>116.46</v>
+        <v>124.08</v>
       </c>
       <c r="I76" t="n">
         <v>0.8200000000000003</v>
       </c>
       <c r="J76" t="n">
-        <v>10.25</v>
+        <v>10.13</v>
       </c>
       <c r="K76" t="n">
-        <v>75.02000000000001</v>
+        <v>73.93999999999998</v>
       </c>
       <c r="L76" t="n">
-        <v>0.64</v>
+        <v>0.5199999999999999</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -16110,7 +16110,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -16167,18 +16167,18 @@
         <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>47.032</v>
+        <v>45.899</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -16199,19 +16199,19 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>124.08</v>
+        <v>167.06</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8200000000000003</v>
+        <v>1.22</v>
       </c>
       <c r="J77" t="n">
-        <v>10.13</v>
+        <v>5.92</v>
       </c>
       <c r="K77" t="n">
-        <v>73.93999999999998</v>
+        <v>42.02999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5199999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -16223,7 +16223,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -16280,18 +16280,18 @@
         <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>45.899</v>
+        <v>43.58700000000001</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -16312,19 +16312,19 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>167.06</v>
+        <v>168.32</v>
       </c>
       <c r="I78" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="J78" t="n">
-        <v>5.92</v>
+        <v>5.810000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>42.02999999999999</v>
+        <v>43.25</v>
       </c>
       <c r="L78" t="n">
-        <v>0.41</v>
+        <v>0.08</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -16336,7 +16336,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0.15</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -16393,18 +16393,18 @@
         <v>0</v>
       </c>
       <c r="AI78" t="n">
-        <v>77</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Patrick Taylor</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>43.58700000000001</v>
+        <v>41.97</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -16425,19 +16425,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>168.32</v>
+        <v>125.48</v>
       </c>
       <c r="I79" t="n">
-        <v>1.17</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>5.810000000000001</v>
+        <v>7.68</v>
       </c>
       <c r="K79" t="n">
-        <v>43.25</v>
+        <v>50.62</v>
       </c>
       <c r="L79" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -16506,18 +16506,18 @@
         <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Patrick Taylor</t>
+          <t>Tyler Goodson</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>41.97</v>
+        <v>41.17100000000001</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -16538,19 +16538,19 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>125.48</v>
+        <v>98.77</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9500000000000001</v>
+        <v>0.6700000000000002</v>
       </c>
       <c r="J80" t="n">
-        <v>7.68</v>
+        <v>8.780000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>50.62</v>
+        <v>65.94000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>0.28</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.21</v>
+        <v>0.05</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -16619,18 +16619,18 @@
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tyler Goodson</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -16639,7 +16639,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>41.17100000000001</v>
+        <v>39.116</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -16651,19 +16651,19 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>98.77</v>
+        <v>81.41</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6700000000000002</v>
+        <v>0.5900000000000002</v>
       </c>
       <c r="J81" t="n">
-        <v>8.780000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>65.94000000000001</v>
+        <v>72.25</v>
       </c>
       <c r="L81" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -16675,7 +16675,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -16732,18 +16732,18 @@
         <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Raheem Blackshear</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -16752,7 +16752,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>39.116</v>
+        <v>37.9116</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -16764,22 +16764,22 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>81.41</v>
+        <v>87.77000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5900000000000002</v>
+        <v>0.32</v>
       </c>
       <c r="J82" t="n">
-        <v>9.789999999999999</v>
+        <v>7.589999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>72.25</v>
+        <v>57.13</v>
       </c>
       <c r="L82" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>76.28999999999999</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -16788,7 +16788,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -16845,18 +16845,18 @@
         <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Raheem Blackshear</t>
+          <t>Craig Reynolds</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16865,7 +16865,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>37.9116</v>
+        <v>35.581</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -16877,22 +16877,22 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>87.77000000000001</v>
+        <v>88.83000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>0.32</v>
+        <v>0.64</v>
       </c>
       <c r="J83" t="n">
-        <v>7.589999999999999</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>57.13</v>
+        <v>53.58</v>
       </c>
       <c r="L83" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="M83" t="n">
-        <v>76.28999999999999</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -16958,18 +16958,18 @@
         <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Craig Reynolds</t>
+          <t>DeeJay Dallas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>35.581</v>
+        <v>35.52680000000001</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -16990,22 +16990,22 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>88.83000000000001</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="J84" t="n">
-        <v>7.140000000000001</v>
+        <v>5.830000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>53.58</v>
+        <v>41.96</v>
       </c>
       <c r="L84" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>170.72</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -17014,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -17071,18 +17071,18 @@
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DeeJay Dallas</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>35.52680000000001</v>
+        <v>35.026</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -17103,22 +17103,22 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>68.81999999999999</v>
+        <v>123.15</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2</v>
+        <v>1.32</v>
       </c>
       <c r="J85" t="n">
-        <v>5.830000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="K85" t="n">
-        <v>41.96</v>
+        <v>17.11</v>
       </c>
       <c r="L85" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>170.72</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -17127,7 +17127,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -17184,18 +17184,18 @@
         <v>0</v>
       </c>
       <c r="AI85" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Chris Brooks</t>
+          <t>Sincere McCormick</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -17204,7 +17204,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35.026</v>
+        <v>34.849</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -17216,19 +17216,19 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>123.15</v>
+        <v>133.48</v>
       </c>
       <c r="I86" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="J86" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="K86" t="n">
-        <v>17.11</v>
+        <v>16.91</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -17240,7 +17240,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -17297,18 +17297,18 @@
         <v>0</v>
       </c>
       <c r="AI86" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sincere McCormick</t>
+          <t>Kenny McIntosh</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -17317,7 +17317,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>34.849</v>
+        <v>34.184</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -17329,19 +17329,19 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>133.48</v>
+        <v>118.37</v>
       </c>
       <c r="I87" t="n">
-        <v>1.18</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>2.62</v>
+        <v>4.85</v>
       </c>
       <c r="K87" t="n">
-        <v>16.91</v>
+        <v>36.17</v>
       </c>
       <c r="L87" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -17353,7 +17353,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -17410,18 +17410,18 @@
         <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>42</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kenny McIntosh</t>
+          <t>Will Shipley</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -17430,7 +17430,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>34.184</v>
+        <v>32.926</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -17442,19 +17442,19 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>118.37</v>
+        <v>85.88000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.5400000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>4.85</v>
+        <v>5.43</v>
       </c>
       <c r="K88" t="n">
-        <v>36.17</v>
+        <v>41.38</v>
       </c>
       <c r="L88" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -17466,7 +17466,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -17523,18 +17523,18 @@
         <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Will Shipley</t>
+          <t>Hassan Haskins</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>32.926</v>
+        <v>32.631</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -17555,19 +17555,19 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>85.88000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5400000000000001</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>5.43</v>
+        <v>4.99</v>
       </c>
       <c r="K89" t="n">
-        <v>41.38</v>
+        <v>32.91</v>
       </c>
       <c r="L89" t="n">
-        <v>0.33</v>
+        <v>0.16</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -17636,18 +17636,18 @@
         <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hassan Haskins</t>
+          <t>Jordan Mims</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -17656,7 +17656,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>32.631</v>
+        <v>28.553</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -17668,19 +17668,19 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>95.3</v>
+        <v>78.60000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6900000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="J90" t="n">
-        <v>4.99</v>
+        <v>4.13</v>
       </c>
       <c r="K90" t="n">
-        <v>32.91</v>
+        <v>23.93</v>
       </c>
       <c r="L90" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -17692,7 +17692,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -17749,13 +17749,13 @@
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>166</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jordan Mims</t>
+          <t>Julius Chestnut</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>28.553</v>
+        <v>28.336</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -17781,32 +17781,32 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>78.60000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="I91" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="J91" t="n">
-        <v>4.13</v>
+        <v>3.43</v>
       </c>
       <c r="K91" t="n">
-        <v>23.93</v>
+        <v>24.8</v>
       </c>
       <c r="L91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
         <v>0.05</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0.02</v>
-      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -17862,18 +17862,18 @@
         <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Julius Chestnut</t>
+          <t>Michael Carter</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -17882,7 +17882,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.336</v>
+        <v>27.878</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -17894,19 +17894,19 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>100.46</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="J92" t="n">
-        <v>3.43</v>
+        <v>4.51</v>
       </c>
       <c r="K92" t="n">
-        <v>24.8</v>
+        <v>29.84</v>
       </c>
       <c r="L92" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -17918,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -17975,18 +17975,18 @@
         <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>163</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Michael Carter</t>
+          <t>Chris Rodriguez</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>27.878</v>
+        <v>27.43500000000001</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -18007,19 +18007,19 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>72.54000000000001</v>
+        <v>104.36</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="J93" t="n">
-        <v>4.51</v>
+        <v>1.21</v>
       </c>
       <c r="K93" t="n">
-        <v>29.84</v>
+        <v>8.59</v>
       </c>
       <c r="L93" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -18031,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -18088,18 +18088,18 @@
         <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>35</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>JaMycal Hasty</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -18108,7 +18108,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>27.43500000000001</v>
+        <v>27.241</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -18120,32 +18120,32 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>104.36</v>
+        <v>67.69999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="J94" t="n">
-        <v>1.21</v>
+        <v>4.21</v>
       </c>
       <c r="K94" t="n">
-        <v>8.59</v>
+        <v>31.51</v>
       </c>
       <c r="L94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
         <v>0.01</v>
       </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0.02</v>
-      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
@@ -18201,18 +18201,18 @@
         <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JaMycal Hasty</t>
+          <t>Ronnie Rivers</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>LAR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -18221,7 +18221,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>27.241</v>
+        <v>25.561</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -18233,19 +18233,19 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>67.69999999999999</v>
+        <v>70.23000000000002</v>
       </c>
       <c r="I95" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="J95" t="n">
-        <v>4.21</v>
+        <v>3.16</v>
       </c>
       <c r="K95" t="n">
-        <v>31.51</v>
+        <v>20.28</v>
       </c>
       <c r="L95" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -18257,7 +18257,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -18314,18 +18314,18 @@
         <v>0</v>
       </c>
       <c r="AI95" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ronnie Rivers</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LAR</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -18334,7 +18334,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>25.561</v>
+        <v>25.292</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -18346,19 +18346,19 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>70.23000000000002</v>
+        <v>56.98</v>
       </c>
       <c r="I96" t="n">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="J96" t="n">
-        <v>3.16</v>
+        <v>3.71</v>
       </c>
       <c r="K96" t="n">
-        <v>20.28</v>
+        <v>28.44</v>
       </c>
       <c r="L96" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -18370,7 +18370,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
@@ -18427,18 +18427,18 @@
         <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -18447,7 +18447,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>25.292</v>
+        <v>23.705</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -18459,19 +18459,19 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>56.98</v>
+        <v>56.13</v>
       </c>
       <c r="I97" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="J97" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="K97" t="n">
-        <v>28.44</v>
+        <v>26.12</v>
       </c>
       <c r="L97" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -18540,18 +18540,18 @@
         <v>0</v>
       </c>
       <c r="AI97" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Dylan Laube</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -18560,7 +18560,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>23.705</v>
+        <v>23.457</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -18572,19 +18572,19 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>56.13</v>
+        <v>53.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="J98" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="K98" t="n">
-        <v>26.12</v>
+        <v>24.77</v>
       </c>
       <c r="L98" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -18596,7 +18596,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -18653,18 +18653,18 @@
         <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dylan Laube</t>
+          <t>Jeff Wilson</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -18673,7 +18673,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>23.457</v>
+        <v>23.049</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -18685,19 +18685,19 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>53.2</v>
+        <v>57.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
       <c r="J99" t="n">
-        <v>3.36</v>
+        <v>2.36</v>
       </c>
       <c r="K99" t="n">
-        <v>24.77</v>
+        <v>17.1</v>
       </c>
       <c r="L99" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -18709,7 +18709,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -18766,18 +18766,18 @@
         <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Jeff Wilson</t>
+          <t>Deuce Vaughn</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -18786,7 +18786,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>23.049</v>
+        <v>21.853</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -18798,19 +18798,19 @@
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>57.09</v>
+        <v>44.23</v>
       </c>
       <c r="I100" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
       <c r="J100" t="n">
-        <v>2.36</v>
+        <v>2.93</v>
       </c>
       <c r="K100" t="n">
-        <v>17.1</v>
+        <v>22.6</v>
       </c>
       <c r="L100" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -18879,18 +18879,18 @@
         <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Deuce Vaughn</t>
+          <t>Mike Boone</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>21.853</v>
+        <v>20.723</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -18911,19 +18911,19 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>44.23</v>
+        <v>41.13</v>
       </c>
       <c r="I101" t="n">
-        <v>0.33</v>
+        <v>0.52</v>
       </c>
       <c r="J101" t="n">
-        <v>2.93</v>
+        <v>2.01</v>
       </c>
       <c r="K101" t="n">
-        <v>22.6</v>
+        <v>12.1</v>
       </c>
       <c r="L101" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -18992,7 +18992,7 @@
         <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -28347,7 +28347,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -49317,7 +49317,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -49329,22 +49329,22 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -49353,7 +49353,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -49410,7 +49410,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -49420,7 +49420,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -49432,19 +49432,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G4" t="n">
         <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I4" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J4" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K4" t="n">
         <v>44</v>
@@ -49513,7 +49513,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
